--- a/enhancements/test-files/04_ARR_pc0101_2026_Sep_newcols.xlsx
+++ b/enhancements/test-files/04_ARR_pc0101_2026_Sep_newcols.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -433,6 +433,13 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +490,41 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -498,12 +540,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -512,18 +554,47 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15265.98</v>
+        <v>16354.57</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46270</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1962.55</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1099.03</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0672</v>
+      </c>
+      <c r="P2" t="n">
+        <v>863.52</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -536,12 +607,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,20 +621,45 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18301.15</v>
+        <v>8047.78</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46203</v>
+        <v>46007</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>965.73</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>627.72</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="P3" t="n">
+        <v>338.01</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Renewal</t>
         </is>
       </c>
     </row>
@@ -578,12 +674,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -592,22 +688,43 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10188.68</v>
+        <v>22897.48</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46281</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46010</v>
+        <v>46087</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>New business</t>
-        </is>
-      </c>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>2747.7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1840.96</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="P4" t="n">
+        <v>906.74</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -620,12 +737,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -634,20 +751,45 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>14682.09</v>
+        <v>20709.49</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46284</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46084</v>
+        <v>46042</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Renewal</t>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2485.14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1590.49</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="P5" t="n">
+        <v>894.65</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
         </is>
       </c>
     </row>
@@ -667,7 +809,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -676,18 +818,43 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>17125.43</v>
+        <v>11348.39</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46287</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46214</v>
+        <v>46108</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>46282</v>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1361.81</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>749</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="P6" t="n">
+        <v>612.8099999999999</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Endorsement</t>
         </is>
